--- a/data/PopCompData_CUrrentCleanedVariables_Apr2026.xlsx
+++ b/data/PopCompData_CUrrentCleanedVariables_Apr2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\You-Shan\Documents\_Projet Ideas 2025\Population Data Comparison 2025\Pop Comparison EuroQol Data Working\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA8293D-181C-4980-8F38-EE17BEDD159D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2B4D74-F78A-4C58-82EF-82ADB393C83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{960E80FA-A2C7-4BB3-8421-6C6091D71274}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
   <si>
     <t xml:space="preserve">age7cat </t>
   </si>
@@ -176,9 +176,6 @@
     <t>Anxiety depression (binary)</t>
   </si>
   <si>
-    <t>No problems on any of 5 items</t>
-  </si>
-  <si>
     <t>EQ-5D utility weighted score</t>
   </si>
   <si>
@@ -255,13 +252,79 @@
   </si>
   <si>
     <t>sex (male, female)</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>DAPHNIE only: region of England</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>Binary: No problems on any of 5 items</t>
+  </si>
+  <si>
+    <t>***only over 18</t>
+  </si>
+  <si>
+    <t>svy_wt</t>
+  </si>
+  <si>
+    <t>Survey Smapling Weight</t>
+  </si>
+  <si>
+    <t>HSE 2017, HSE 2018, DAPHNIE 2023, DAPHNIE 2024</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>All except DAPHNIE 2023</t>
+  </si>
+  <si>
+    <t>Comparable (yes no)</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>yes, higher degree v no</t>
+  </si>
+  <si>
+    <t>yes, white/not white</t>
+  </si>
+  <si>
+    <t>maybe, later</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ill_dis </t>
+  </si>
+  <si>
+    <t>meds_num</t>
+  </si>
+  <si>
+    <t>presence of illness (past year or half year)</t>
+  </si>
+  <si>
+    <t>maybe?</t>
+  </si>
+  <si>
+    <t>number of medications taken</t>
+  </si>
+  <si>
+    <t>??</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,16 +333,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -309,18 +385,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,315 +730,481 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453072BE-2A64-4A1B-8CA5-F303D637AF70}">
-  <dimension ref="D3:E68"/>
+  <dimension ref="A3:E69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="32.26953125" customWidth="1"/>
-    <col min="5" max="5" width="24.08984375" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" customWidth="1"/>
+    <col min="4" max="4" width="32.26953125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D4" s="1" t="s">
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D28" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D7" s="2" t="s">
+      <c r="E29" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D35" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D27" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D28" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D29" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D34" s="3" t="s">
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" t="s">
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" t="s">
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" t="s">
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D39" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D38" s="3" t="s">
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" t="s">
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" t="s">
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" t="s">
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D42" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" t="s">
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" t="s">
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="4:5" ht="16" x14ac:dyDescent="0.35">
-      <c r="D44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="4:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="D68" s="1" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D69" s="2" t="s">
         <v>0</v>
       </c>
     </row>
